--- a/patient.xlsx
+++ b/patient.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ilyachermnykh/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ilyachermnykh/Desktop/Новая папка 3/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{491CF8D4-41AB-934E-A3DC-689DDD3C1374}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{644F113D-1C7A-B44A-A486-7983BE094978}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="16260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="16220" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="passport" sheetId="1" r:id="rId1"/>
@@ -2212,11 +2212,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -2251,6 +2252,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr lang="en"/>
               <a:t>total cholesterol</a:t>
             </a:r>
           </a:p>
@@ -2393,6 +2395,7 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
+                  <a:rPr lang="ru-RU"/>
                   <a:t>Дата</a:t>
                 </a:r>
               </a:p>
@@ -2429,6 +2432,7 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
+                  <a:rPr lang="ru-RU"/>
                   <a:t>Значение</a:t>
                 </a:r>
               </a:p>
@@ -4025,6 +4029,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr lang="en"/>
               <a:t>hdl</a:t>
             </a:r>
           </a:p>
@@ -4161,6 +4166,7 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
+                  <a:rPr lang="ru-RU"/>
                   <a:t>Дата</a:t>
                 </a:r>
               </a:p>
@@ -4197,6 +4203,7 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
+                  <a:rPr lang="ru-RU"/>
                   <a:t>Значение</a:t>
                 </a:r>
               </a:p>
@@ -4246,6 +4253,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr lang="en"/>
               <a:t>triglycerides</a:t>
             </a:r>
           </a:p>
@@ -4388,6 +4396,7 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
+                  <a:rPr lang="ru-RU"/>
                   <a:t>Дата</a:t>
                 </a:r>
               </a:p>
@@ -4424,6 +4433,7 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
+                  <a:rPr lang="ru-RU"/>
                   <a:t>Значение</a:t>
                 </a:r>
               </a:p>
@@ -4473,6 +4483,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr lang="en"/>
               <a:t>hba1c</a:t>
             </a:r>
           </a:p>
@@ -4609,6 +4620,7 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
+                  <a:rPr lang="ru-RU"/>
                   <a:t>Дата</a:t>
                 </a:r>
               </a:p>
@@ -4645,6 +4657,7 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
+                  <a:rPr lang="ru-RU"/>
                   <a:t>Значение</a:t>
                 </a:r>
               </a:p>
@@ -6366,6 +6379,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="10.1640625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
@@ -6449,6 +6465,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="10.1640625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
@@ -6538,8 +6557,11 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="10.1640625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
@@ -6611,6 +6633,14 @@
       </c>
       <c r="B9">
         <v>6.1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A10" s="2">
+        <v>46184</v>
+      </c>
+      <c r="B10">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/patient.xlsx
+++ b/patient.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ilyachermnykh/Desktop/Новая папка 3/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{644F113D-1C7A-B44A-A486-7983BE094978}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C891066-E9A4-7849-A0E4-8B34C22723AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="16220" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4521,9 +4521,9 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>graph_hba1c!$A$2:$A$9</c:f>
+              <c:f>graph_hba1c!$A$2:$A$10</c:f>
               <c:strCache>
-                <c:ptCount val="8"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>2020-12-02</c:v>
                 </c:pt>
@@ -4547,16 +4547,19 @@
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>2026-05-11</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>22.05.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>graph_hba1c!$B$2:$B$9</c:f>
+              <c:f>graph_hba1c!$B$2:$B$10</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>5.7</c:v>
                 </c:pt>
@@ -4580,6 +4583,9 @@
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>6.1</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>3</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6557,7 +6563,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.1640625" bestFit="1" customWidth="1"/>
@@ -6637,11 +6643,14 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" s="2">
-        <v>46184</v>
+        <v>46164</v>
       </c>
       <c r="B10">
-        <v>0</v>
-      </c>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A12" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
